--- a/Fines Record - Tracker 2026.xlsx
+++ b/Fines Record - Tracker 2026.xlsx
@@ -6,12 +6,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuvra\Downloads\BMSSCL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PatilY\source\personal\PC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF4B508-8F1E-42D4-8EB6-091B7168DECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158DBDFD-0770-4E53-BE85-8581D8720D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Live" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="111">
   <si>
     <t>Third+ Offence</t>
   </si>
@@ -528,6 +528,9 @@
   <si>
     <t>15a(£5)</t>
   </si>
+  <si>
+    <t>Rule Discription</t>
+  </si>
 </sst>
 </file>
 
@@ -536,7 +539,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$£]#,##0.00"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -674,12 +677,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -1073,7 +1070,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1329,38 +1326,9 @@
     <xf numFmtId="16" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="18" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="18" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="18" fillId="33" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1398,7 +1366,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1427,10 +1395,10 @@
     <xf numFmtId="0" fontId="7" fillId="26" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1489,7 +1457,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1503,6 +1471,38 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="18" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="18" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="18" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="18" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="18" fillId="33" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1764,43 +1764,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ1003"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="8.5703125" customWidth="1"/>
-    <col min="11" max="12" width="8.140625" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" customWidth="1"/>
-    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" customWidth="1"/>
-    <col min="17" max="17" width="8.5703125" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" customWidth="1"/>
-    <col min="21" max="22" width="8.140625" customWidth="1"/>
-    <col min="23" max="23" width="7.85546875" customWidth="1"/>
-    <col min="24" max="25" width="8.5703125" customWidth="1"/>
-    <col min="26" max="26" width="9.42578125" customWidth="1"/>
-    <col min="27" max="27" width="8.5703125" customWidth="1"/>
-    <col min="28" max="28" width="9.5703125" customWidth="1"/>
-    <col min="29" max="49" width="8.5703125" customWidth="1"/>
-    <col min="50" max="50" width="8.28515625" customWidth="1"/>
-    <col min="51" max="52" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="8.5546875" customWidth="1"/>
+    <col min="11" max="12" width="8.109375" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" customWidth="1"/>
+    <col min="17" max="17" width="8.5546875" customWidth="1"/>
+    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="19" max="19" width="7.33203125" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" customWidth="1"/>
+    <col min="21" max="22" width="8.109375" customWidth="1"/>
+    <col min="23" max="23" width="7.88671875" customWidth="1"/>
+    <col min="24" max="25" width="8.5546875" customWidth="1"/>
+    <col min="26" max="26" width="9.44140625" customWidth="1"/>
+    <col min="27" max="27" width="8.5546875" customWidth="1"/>
+    <col min="28" max="28" width="9.5546875" customWidth="1"/>
+    <col min="29" max="49" width="8.5546875" customWidth="1"/>
+    <col min="50" max="50" width="8.33203125" customWidth="1"/>
+    <col min="51" max="52" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:51" ht="21" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>77</v>
       </c>
       <c r="AD1" s="2"/>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="S2" s="3" t="s">
@@ -1813,79 +1813,79 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51" s="51" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" s="51" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B3" s="37" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="118">
+      <c r="D3" s="166">
         <v>46113</v>
       </c>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157" t="s">
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="146"/>
+      <c r="I3" s="146" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="113">
+      <c r="J3" s="162">
         <v>46143</v>
       </c>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="111"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="161"/>
       <c r="O3" s="53"/>
       <c r="P3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="Q3" s="54"/>
       <c r="R3" s="54"/>
-      <c r="S3" s="114">
+      <c r="S3" s="163">
         <v>46174</v>
       </c>
-      <c r="T3" s="110"/>
-      <c r="U3" s="110"/>
-      <c r="V3" s="110"/>
-      <c r="W3" s="110"/>
-      <c r="X3" s="110"/>
-      <c r="Y3" s="110"/>
-      <c r="Z3" s="111"/>
+      <c r="T3" s="160"/>
+      <c r="U3" s="160"/>
+      <c r="V3" s="160"/>
+      <c r="W3" s="160"/>
+      <c r="X3" s="160"/>
+      <c r="Y3" s="160"/>
+      <c r="Z3" s="161"/>
       <c r="AA3" s="54"/>
       <c r="AB3" s="54"/>
       <c r="AC3" s="55" t="s">
         <v>5</v>
       </c>
       <c r="AD3" s="56"/>
-      <c r="AE3" s="115">
+      <c r="AE3" s="164">
         <v>46204</v>
       </c>
-      <c r="AF3" s="110"/>
-      <c r="AG3" s="110"/>
-      <c r="AH3" s="111"/>
+      <c r="AF3" s="160"/>
+      <c r="AG3" s="160"/>
+      <c r="AH3" s="161"/>
       <c r="AI3" s="57"/>
       <c r="AJ3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="116">
+      <c r="AK3" s="165">
         <v>46235</v>
       </c>
-      <c r="AL3" s="110"/>
-      <c r="AM3" s="110"/>
-      <c r="AN3" s="110"/>
-      <c r="AO3" s="111"/>
+      <c r="AL3" s="160"/>
+      <c r="AM3" s="160"/>
+      <c r="AN3" s="160"/>
+      <c r="AO3" s="161"/>
       <c r="AP3" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="AQ3" s="109">
+      <c r="AQ3" s="159">
         <v>46266</v>
       </c>
-      <c r="AR3" s="110"/>
-      <c r="AS3" s="110"/>
-      <c r="AT3" s="110"/>
-      <c r="AU3" s="111"/>
+      <c r="AR3" s="160"/>
+      <c r="AS3" s="160"/>
+      <c r="AT3" s="160"/>
+      <c r="AU3" s="161"/>
       <c r="AV3" s="59" t="s">
         <v>5</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:51" s="51" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" s="51" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="B4" s="37" t="s">
         <v>9</v>
       </c>
@@ -1915,11 +1915,11 @@
       <c r="F4" s="106">
         <v>45772</v>
       </c>
-      <c r="G4" s="117"/>
+      <c r="G4" s="107"/>
       <c r="H4" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="158"/>
+      <c r="I4" s="147"/>
       <c r="J4" s="40">
         <v>45780</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="AX4" s="39"/>
       <c r="AY4" s="39"/>
     </row>
-    <row r="5" spans="1:51" s="51" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" s="51" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="51" t="s">
         <v>96</v>
       </c>
@@ -2047,7 +2047,7 @@
       <c r="H5" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="159"/>
+      <c r="I5" s="148"/>
       <c r="J5" s="62"/>
       <c r="K5" s="62"/>
       <c r="L5" s="62"/>
@@ -2097,11 +2097,11 @@
       <c r="AX5" s="62"/>
       <c r="AY5" s="62"/>
     </row>
-    <row r="6" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="160">
+    <row r="6" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="149">
         <v>1</v>
       </c>
-      <c r="B6" s="161" t="s">
+      <c r="B6" s="150" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="105"/>
@@ -2158,11 +2158,11 @@
       <c r="AX6" s="21"/>
       <c r="AY6" s="21"/>
     </row>
-    <row r="7" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="160">
+    <row r="7" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="149">
         <v>2</v>
       </c>
-      <c r="B7" s="161" t="s">
+      <c r="B7" s="150" t="s">
         <v>97</v>
       </c>
       <c r="C7" s="105"/>
@@ -2215,11 +2215,11 @@
       <c r="AX7" s="21"/>
       <c r="AY7" s="21"/>
     </row>
-    <row r="8" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="160">
+    <row r="8" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="149">
         <v>3</v>
       </c>
-      <c r="B8" s="161" t="s">
+      <c r="B8" s="150" t="s">
         <v>98</v>
       </c>
       <c r="C8" s="105"/>
@@ -2272,11 +2272,11 @@
       <c r="AX8" s="21"/>
       <c r="AY8" s="21"/>
     </row>
-    <row r="9" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="160">
+    <row r="9" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="149">
         <v>4</v>
       </c>
-      <c r="B9" s="161" t="s">
+      <c r="B9" s="150" t="s">
         <v>99</v>
       </c>
       <c r="C9" s="105"/>
@@ -2329,11 +2329,11 @@
       <c r="AX9" s="21"/>
       <c r="AY9" s="21"/>
     </row>
-    <row r="10" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="160">
+    <row r="10" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="149">
         <v>5</v>
       </c>
-      <c r="B10" s="162" t="s">
+      <c r="B10" s="151" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="105"/>
@@ -2390,11 +2390,11 @@
       <c r="AX10" s="21"/>
       <c r="AY10" s="21"/>
     </row>
-    <row r="11" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="160">
+    <row r="11" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="149">
         <v>6</v>
       </c>
-      <c r="B11" s="161" t="s">
+      <c r="B11" s="150" t="s">
         <v>79</v>
       </c>
       <c r="C11" s="105"/>
@@ -2447,20 +2447,20 @@
       <c r="AX11" s="21"/>
       <c r="AY11" s="21"/>
     </row>
-    <row r="12" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="160">
+    <row r="12" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="149">
         <v>7</v>
       </c>
-      <c r="B12" s="161" t="s">
+      <c r="B12" s="150" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="134"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="152"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="124"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="124"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="141"/>
       <c r="J12" s="76"/>
       <c r="K12" s="76"/>
       <c r="L12" s="70"/>
@@ -2504,20 +2504,20 @@
       <c r="AX12" s="21"/>
       <c r="AY12" s="21"/>
     </row>
-    <row r="13" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="160">
+    <row r="13" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="149">
         <v>8</v>
       </c>
-      <c r="B13" s="161" t="s">
+      <c r="B13" s="150" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="134"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="153"/>
+      <c r="C13" s="123"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="124"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="142"/>
       <c r="J13" s="88"/>
       <c r="K13" s="70"/>
       <c r="L13" s="70"/>
@@ -2561,20 +2561,20 @@
       <c r="AX13" s="21"/>
       <c r="AY13" s="21"/>
     </row>
-    <row r="14" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="160">
+    <row r="14" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="149">
         <v>9</v>
       </c>
-      <c r="B14" s="161" t="s">
+      <c r="B14" s="150" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="134"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="140"/>
-      <c r="G14" s="140"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="154"/>
+      <c r="C14" s="123"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="128"/>
+      <c r="I14" s="143"/>
       <c r="J14" s="88"/>
       <c r="K14" s="70"/>
       <c r="L14" s="70"/>
@@ -2618,20 +2618,20 @@
       <c r="AX14" s="21"/>
       <c r="AY14" s="21"/>
     </row>
-    <row r="15" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="160">
+    <row r="15" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="149">
         <v>10</v>
       </c>
-      <c r="B15" s="162" t="s">
+      <c r="B15" s="151" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="134"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="152"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="141"/>
       <c r="J15" s="86"/>
       <c r="K15" s="76"/>
       <c r="L15" s="86"/>
@@ -2675,22 +2675,22 @@
       <c r="AX15" s="21"/>
       <c r="AY15" s="21"/>
     </row>
-    <row r="16" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="160">
+    <row r="16" spans="1:51" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="149">
         <v>11</v>
       </c>
-      <c r="B16" s="161" t="s">
+      <c r="B16" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="134"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="140" t="s">
+      <c r="C16" s="123"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="129" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="140"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="154">
+      <c r="F16" s="129"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="128"/>
+      <c r="I16" s="143">
         <v>10</v>
       </c>
       <c r="J16" s="76"/>
@@ -2736,20 +2736,20 @@
       <c r="AX16" s="21"/>
       <c r="AY16" s="21"/>
     </row>
-    <row r="17" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="160">
+    <row r="17" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="149">
         <v>12</v>
       </c>
-      <c r="B17" s="161" t="s">
+      <c r="B17" s="150" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="142"/>
-      <c r="D17" s="135"/>
-      <c r="E17" s="135"/>
-      <c r="F17" s="135"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="141"/>
-      <c r="I17" s="154"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="143"/>
       <c r="J17" s="76"/>
       <c r="K17" s="70"/>
       <c r="L17" s="70"/>
@@ -2793,24 +2793,24 @@
       <c r="AX17" s="21"/>
       <c r="AY17" s="21"/>
     </row>
-    <row r="18" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="160">
+    <row r="18" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="149">
         <v>13</v>
       </c>
-      <c r="B18" s="161" t="s">
+      <c r="B18" s="150" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="134"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="138" t="s">
+      <c r="C18" s="123"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="127" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="143" t="s">
+      <c r="F18" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="G18" s="135"/>
-      <c r="H18" s="136"/>
-      <c r="I18" s="152">
+      <c r="G18" s="124"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="141">
         <v>10</v>
       </c>
       <c r="J18" s="70"/>
@@ -2856,22 +2856,22 @@
       <c r="AX18" s="21"/>
       <c r="AY18" s="21"/>
     </row>
-    <row r="19" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="160">
+    <row r="19" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="149">
         <v>14</v>
       </c>
-      <c r="B19" s="161" t="s">
+      <c r="B19" s="150" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="134"/>
-      <c r="D19" s="135"/>
-      <c r="E19" s="135"/>
-      <c r="F19" s="143" t="s">
+      <c r="C19" s="123"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="132" t="s">
         <v>109</v>
       </c>
-      <c r="G19" s="135"/>
-      <c r="H19" s="136"/>
-      <c r="I19" s="152">
+      <c r="G19" s="124"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="141">
         <v>5</v>
       </c>
       <c r="J19" s="70"/>
@@ -2917,22 +2917,22 @@
       <c r="AX19" s="21"/>
       <c r="AY19" s="21"/>
     </row>
-    <row r="20" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="160">
+    <row r="20" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="149">
         <v>15</v>
       </c>
-      <c r="B20" s="161" t="s">
+      <c r="B20" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="134"/>
-      <c r="D20" s="135"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="144" t="s">
+      <c r="C20" s="123"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="133" t="s">
         <v>108</v>
       </c>
-      <c r="G20" s="135"/>
-      <c r="H20" s="139"/>
-      <c r="I20" s="154">
+      <c r="G20" s="124"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="143">
         <v>10</v>
       </c>
       <c r="J20" s="70"/>
@@ -2978,20 +2978,20 @@
       <c r="AX20" s="21"/>
       <c r="AY20" s="21"/>
     </row>
-    <row r="21" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="160">
+    <row r="21" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="149">
         <v>16</v>
       </c>
-      <c r="B21" s="161" t="s">
+      <c r="B21" s="150" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="134"/>
-      <c r="D21" s="135"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="135"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="136"/>
-      <c r="I21" s="152"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="124"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="124"/>
+      <c r="G21" s="124"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="141"/>
       <c r="J21" s="70"/>
       <c r="K21" s="70"/>
       <c r="L21" s="79"/>
@@ -3035,22 +3035,22 @@
       <c r="AX21" s="21"/>
       <c r="AY21" s="21"/>
     </row>
-    <row r="22" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="160">
+    <row r="22" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="149">
         <v>17</v>
       </c>
-      <c r="B22" s="161" t="s">
+      <c r="B22" s="150" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="134"/>
-      <c r="D22" s="135"/>
-      <c r="E22" s="145"/>
-      <c r="F22" s="135" t="s">
+      <c r="C22" s="123"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="134"/>
+      <c r="F22" s="124" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="145"/>
-      <c r="H22" s="139"/>
-      <c r="I22" s="155">
+      <c r="G22" s="134"/>
+      <c r="H22" s="128"/>
+      <c r="I22" s="144">
         <v>10</v>
       </c>
       <c r="J22" s="88"/>
@@ -3096,20 +3096,20 @@
       <c r="AX22" s="21"/>
       <c r="AY22" s="21"/>
     </row>
-    <row r="23" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="160">
+    <row r="23" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="149">
         <v>18</v>
       </c>
-      <c r="B23" s="161" t="s">
+      <c r="B23" s="150" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="134"/>
-      <c r="D23" s="135"/>
-      <c r="E23" s="135"/>
-      <c r="F23" s="135"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="152"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="124"/>
+      <c r="G23" s="124"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="141"/>
       <c r="J23" s="70"/>
       <c r="K23" s="76"/>
       <c r="L23" s="70"/>
@@ -3153,20 +3153,20 @@
       <c r="AX23" s="21"/>
       <c r="AY23" s="21"/>
     </row>
-    <row r="24" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="160">
+    <row r="24" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="149">
         <v>19</v>
       </c>
-      <c r="B24" s="161" t="s">
+      <c r="B24" s="150" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="134"/>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="140"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="139"/>
-      <c r="I24" s="154"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="124"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="143"/>
       <c r="J24" s="70"/>
       <c r="K24" s="70"/>
       <c r="L24" s="70"/>
@@ -3210,20 +3210,20 @@
       <c r="AX24" s="21"/>
       <c r="AY24" s="21"/>
     </row>
-    <row r="25" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="160">
+    <row r="25" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="149">
         <v>20</v>
       </c>
-      <c r="B25" s="161" t="s">
+      <c r="B25" s="150" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="134"/>
-      <c r="D25" s="135"/>
-      <c r="E25" s="138"/>
-      <c r="F25" s="135"/>
-      <c r="G25" s="135"/>
-      <c r="H25" s="136"/>
-      <c r="I25" s="152"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="141"/>
       <c r="J25" s="76"/>
       <c r="K25" s="70"/>
       <c r="L25" s="70"/>
@@ -3267,22 +3267,22 @@
       <c r="AX25" s="21"/>
       <c r="AY25" s="21"/>
     </row>
-    <row r="26" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="160">
+    <row r="26" spans="1:52" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="149">
         <v>21</v>
       </c>
-      <c r="B26" s="161" t="s">
+      <c r="B26" s="150" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="146"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="147" t="s">
+      <c r="C26" s="135"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="136" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="147"/>
-      <c r="H26" s="148"/>
-      <c r="I26" s="152">
+      <c r="G26" s="136"/>
+      <c r="H26" s="137"/>
+      <c r="I26" s="141">
         <v>10</v>
       </c>
       <c r="J26" s="70"/>
@@ -3328,121 +3328,121 @@
       <c r="AX26" s="21"/>
       <c r="AY26" s="21"/>
     </row>
-    <row r="27" spans="1:52" s="130" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="163">
+    <row r="27" spans="1:52" s="119" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="152">
         <v>22</v>
       </c>
-      <c r="B27" s="164" t="s">
+      <c r="B27" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="149"/>
-      <c r="D27" s="150"/>
-      <c r="E27" s="150"/>
-      <c r="F27" s="150"/>
-      <c r="G27" s="150"/>
-      <c r="H27" s="151"/>
-      <c r="I27" s="156"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="120"/>
-      <c r="L27" s="120"/>
-      <c r="M27" s="120"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="121"/>
-      <c r="P27" s="122"/>
-      <c r="Q27" s="120"/>
-      <c r="R27" s="123"/>
-      <c r="S27" s="120"/>
-      <c r="T27" s="120"/>
-      <c r="U27" s="120"/>
-      <c r="V27" s="120"/>
-      <c r="W27" s="120"/>
-      <c r="X27" s="120"/>
-      <c r="Y27" s="120"/>
-      <c r="Z27" s="120"/>
-      <c r="AA27" s="120"/>
-      <c r="AB27" s="124"/>
-      <c r="AC27" s="125"/>
-      <c r="AD27" s="126"/>
-      <c r="AE27" s="120"/>
-      <c r="AF27" s="120"/>
-      <c r="AG27" s="120"/>
-      <c r="AH27" s="124"/>
-      <c r="AI27" s="127"/>
-      <c r="AJ27" s="125"/>
-      <c r="AK27" s="120"/>
-      <c r="AL27" s="120"/>
-      <c r="AM27" s="120"/>
-      <c r="AN27" s="120"/>
-      <c r="AO27" s="120"/>
-      <c r="AP27" s="128"/>
-      <c r="AQ27" s="120"/>
-      <c r="AR27" s="120"/>
-      <c r="AS27" s="120"/>
-      <c r="AT27" s="120"/>
-      <c r="AU27" s="120"/>
-      <c r="AV27" s="129"/>
-      <c r="AW27" s="119"/>
-      <c r="AX27" s="119"/>
-      <c r="AY27" s="119"/>
-    </row>
-    <row r="28" spans="1:52" s="132" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="165" t="s">
+      <c r="C27" s="138"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
+      <c r="H27" s="140"/>
+      <c r="I27" s="145"/>
+      <c r="J27" s="109"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="109"/>
+      <c r="M27" s="109"/>
+      <c r="N27" s="109"/>
+      <c r="O27" s="110"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="109"/>
+      <c r="R27" s="112"/>
+      <c r="S27" s="109"/>
+      <c r="T27" s="109"/>
+      <c r="U27" s="109"/>
+      <c r="V27" s="109"/>
+      <c r="W27" s="109"/>
+      <c r="X27" s="109"/>
+      <c r="Y27" s="109"/>
+      <c r="Z27" s="109"/>
+      <c r="AA27" s="109"/>
+      <c r="AB27" s="113"/>
+      <c r="AC27" s="114"/>
+      <c r="AD27" s="115"/>
+      <c r="AE27" s="109"/>
+      <c r="AF27" s="109"/>
+      <c r="AG27" s="109"/>
+      <c r="AH27" s="113"/>
+      <c r="AI27" s="116"/>
+      <c r="AJ27" s="114"/>
+      <c r="AK27" s="109"/>
+      <c r="AL27" s="109"/>
+      <c r="AM27" s="109"/>
+      <c r="AN27" s="109"/>
+      <c r="AO27" s="109"/>
+      <c r="AP27" s="117"/>
+      <c r="AQ27" s="109"/>
+      <c r="AR27" s="109"/>
+      <c r="AS27" s="109"/>
+      <c r="AT27" s="109"/>
+      <c r="AU27" s="109"/>
+      <c r="AV27" s="118"/>
+      <c r="AW27" s="108"/>
+      <c r="AX27" s="108"/>
+      <c r="AY27" s="108"/>
+    </row>
+    <row r="28" spans="1:52" s="121" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="167"/>
-      <c r="D28" s="168"/>
-      <c r="E28" s="168"/>
-      <c r="F28" s="168"/>
-      <c r="G28" s="168"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="166">
+      <c r="C28" s="156"/>
+      <c r="D28" s="157"/>
+      <c r="E28" s="157"/>
+      <c r="F28" s="157"/>
+      <c r="G28" s="157"/>
+      <c r="H28" s="158"/>
+      <c r="I28" s="155">
         <f>SUM(I6:I27)</f>
         <v>75</v>
       </c>
-      <c r="J28" s="133"/>
-      <c r="K28" s="133"/>
-      <c r="L28" s="133"/>
-      <c r="M28" s="133"/>
-      <c r="N28" s="133"/>
-      <c r="O28" s="133"/>
-      <c r="P28" s="133"/>
-      <c r="Q28" s="133"/>
-      <c r="R28" s="133"/>
-      <c r="S28" s="133"/>
-      <c r="T28" s="133"/>
-      <c r="U28" s="133"/>
-      <c r="V28" s="133"/>
-      <c r="W28" s="133"/>
-      <c r="X28" s="133"/>
-      <c r="Y28" s="133"/>
-      <c r="Z28" s="133"/>
-      <c r="AA28" s="133"/>
-      <c r="AB28" s="133"/>
-      <c r="AC28" s="133"/>
-      <c r="AD28" s="133"/>
-      <c r="AE28" s="133"/>
-      <c r="AF28" s="133"/>
-      <c r="AG28" s="133"/>
-      <c r="AH28" s="133"/>
-      <c r="AI28" s="133"/>
-      <c r="AJ28" s="133"/>
-      <c r="AK28" s="133"/>
-      <c r="AL28" s="133"/>
-      <c r="AM28" s="133"/>
-      <c r="AN28" s="133"/>
-      <c r="AO28" s="133"/>
-      <c r="AP28" s="131"/>
-      <c r="AQ28" s="133"/>
-      <c r="AR28" s="133"/>
-      <c r="AS28" s="133"/>
-      <c r="AT28" s="133"/>
-      <c r="AU28" s="133"/>
-      <c r="AV28" s="131"/>
-      <c r="AW28" s="133"/>
-      <c r="AX28" s="133"/>
-      <c r="AY28" s="133"/>
-    </row>
-    <row r="29" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="122"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
+      <c r="M28" s="122"/>
+      <c r="N28" s="122"/>
+      <c r="O28" s="122"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="122"/>
+      <c r="R28" s="122"/>
+      <c r="S28" s="122"/>
+      <c r="T28" s="122"/>
+      <c r="U28" s="122"/>
+      <c r="V28" s="122"/>
+      <c r="W28" s="122"/>
+      <c r="X28" s="122"/>
+      <c r="Y28" s="122"/>
+      <c r="Z28" s="122"/>
+      <c r="AA28" s="122"/>
+      <c r="AB28" s="122"/>
+      <c r="AC28" s="122"/>
+      <c r="AD28" s="122"/>
+      <c r="AE28" s="122"/>
+      <c r="AF28" s="122"/>
+      <c r="AG28" s="122"/>
+      <c r="AH28" s="122"/>
+      <c r="AI28" s="122"/>
+      <c r="AJ28" s="122"/>
+      <c r="AK28" s="122"/>
+      <c r="AL28" s="122"/>
+      <c r="AM28" s="122"/>
+      <c r="AN28" s="122"/>
+      <c r="AO28" s="122"/>
+      <c r="AP28" s="120"/>
+      <c r="AQ28" s="122"/>
+      <c r="AR28" s="122"/>
+      <c r="AS28" s="122"/>
+      <c r="AT28" s="122"/>
+      <c r="AU28" s="122"/>
+      <c r="AV28" s="120"/>
+      <c r="AW28" s="122"/>
+      <c r="AX28" s="122"/>
+      <c r="AY28" s="122"/>
+    </row>
+    <row r="29" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="6"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -3495,154 +3495,158 @@
       <c r="AY29" s="5"/>
       <c r="AZ29" s="5"/>
     </row>
-    <row r="30" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="10" t="s">
         <v>45</v>
       </c>
       <c r="AW31" s="11"/>
     </row>
-    <row r="32" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:52" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
         <v>48</v>
       </c>
+      <c r="C35" s="170" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="4"/>
       <c r="M35" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="M36" s="107" t="s">
+      <c r="M36" s="167" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="107"/>
-      <c r="O36" s="107"/>
-    </row>
-    <row r="37" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N36" s="167"/>
+      <c r="O36" s="167"/>
+    </row>
+    <row r="37" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="M37" s="107" t="s">
+      <c r="M37" s="167" t="s">
         <v>53</v>
       </c>
-      <c r="N37" s="107"/>
-      <c r="O37" s="107"/>
-    </row>
-    <row r="38" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N37" s="167"/>
+      <c r="O37" s="167"/>
+    </row>
+    <row r="38" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="M38" s="107" t="s">
+      <c r="M38" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="N38" s="107"/>
-      <c r="O38" s="107"/>
-    </row>
-    <row r="39" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N38" s="167"/>
+      <c r="O38" s="167"/>
+    </row>
+    <row r="39" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M39" s="107" t="s">
+      <c r="M39" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="N39" s="107"/>
-      <c r="O39" s="107"/>
-    </row>
-    <row r="40" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N39" s="167"/>
+      <c r="O39" s="167"/>
+    </row>
+    <row r="40" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="17" t="s">
         <v>85</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="M40" s="107" t="s">
+      <c r="M40" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="N40" s="107"/>
-      <c r="O40" s="107"/>
-    </row>
-    <row r="41" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N40" s="167"/>
+      <c r="O40" s="167"/>
+    </row>
+    <row r="41" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M41" s="107" t="s">
+      <c r="M41" s="167" t="s">
         <v>59</v>
       </c>
-      <c r="N41" s="107"/>
-      <c r="O41" s="107"/>
-    </row>
-    <row r="42" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N41" s="167"/>
+      <c r="O41" s="167"/>
+    </row>
+    <row r="42" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="M42" s="108" t="s">
+      <c r="M42" s="168" t="s">
         <v>94</v>
       </c>
-      <c r="N42" s="107"/>
-      <c r="O42" s="107"/>
-    </row>
-    <row r="43" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N42" s="167"/>
+      <c r="O42" s="167"/>
+    </row>
+    <row r="43" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M43" s="108" t="s">
+      <c r="M43" s="168" t="s">
         <v>94</v>
       </c>
-      <c r="N43" s="107"/>
-      <c r="O43" s="107"/>
-    </row>
-    <row r="44" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N43" s="167"/>
+      <c r="O43" s="167"/>
+    </row>
+    <row r="44" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M44" s="107" t="s">
+      <c r="M44" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="N44" s="107"/>
-      <c r="O44" s="107"/>
-    </row>
-    <row r="45" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N44" s="167"/>
+      <c r="O44" s="167"/>
+    </row>
+    <row r="45" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="17" t="s">
         <v>90</v>
       </c>
@@ -3653,7 +3657,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>91</v>
       </c>
@@ -3664,1035 +3668,1025 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="17" t="s">
         <v>92</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="M47" s="107" t="s">
+      <c r="M47" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="N47" s="107"/>
-      <c r="O47" s="107"/>
-    </row>
-    <row r="48" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N47" s="167"/>
+      <c r="O47" s="167"/>
+    </row>
+    <row r="48" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="M48" s="107" t="s">
+      <c r="M48" s="167" t="s">
         <v>69</v>
       </c>
-      <c r="N48" s="107"/>
-      <c r="O48" s="107"/>
-    </row>
-    <row r="49" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N48" s="167"/>
+      <c r="O48" s="167"/>
+    </row>
+    <row r="49" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="18" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="M49" s="107" t="s">
+      <c r="M49" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="N49" s="107"/>
-      <c r="O49" s="107"/>
-    </row>
-    <row r="50" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N49" s="167"/>
+      <c r="O49" s="167"/>
+    </row>
+    <row r="50" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="19" t="s">
         <v>73</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="M50" s="107" t="s">
+      <c r="M50" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="N50" s="107"/>
-      <c r="O50" s="107"/>
-    </row>
-    <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N50" s="167"/>
+      <c r="O50" s="167"/>
+    </row>
+    <row r="51" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="19" t="s">
         <v>75</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="M51" s="107" t="s">
+      <c r="M51" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="N51" s="107"/>
-      <c r="O51" s="107"/>
-    </row>
-    <row r="52" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="N51" s="167"/>
+      <c r="O51" s="167"/>
+    </row>
+    <row r="52" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="AQ3:AU3"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="S3:Z3"/>
-    <mergeCell ref="AE3:AH3"/>
-    <mergeCell ref="AK3:AO3"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="M36:O36"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="M39:O39"/>
     <mergeCell ref="M40:O40"/>
     <mergeCell ref="M50:O50"/>
     <mergeCell ref="M51:O51"/>
@@ -4703,6 +4697,16 @@
     <mergeCell ref="M43:O43"/>
     <mergeCell ref="M44:O44"/>
     <mergeCell ref="M47:O47"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="AQ3:AU3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="S3:Z3"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AK3:AO3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -4713,40 +4717,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEC1EA7-C028-41BE-91BB-3C250A176239}">
   <dimension ref="A1:AY1002"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="8.5703125" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" customWidth="1"/>
-    <col min="20" max="21" width="8.140625" customWidth="1"/>
-    <col min="22" max="22" width="7.85546875" customWidth="1"/>
-    <col min="23" max="24" width="8.5703125" customWidth="1"/>
-    <col min="25" max="25" width="9.42578125" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="27" width="9.5703125" customWidth="1"/>
-    <col min="28" max="48" width="8.5703125" customWidth="1"/>
-    <col min="49" max="49" width="8.28515625" customWidth="1"/>
-    <col min="50" max="51" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="8.5546875" customWidth="1"/>
+    <col min="10" max="11" width="8.109375" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" customWidth="1"/>
+    <col min="15" max="15" width="8.44140625" customWidth="1"/>
+    <col min="16" max="16" width="8.5546875" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" customWidth="1"/>
+    <col min="18" max="18" width="7.33203125" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" customWidth="1"/>
+    <col min="20" max="21" width="8.109375" customWidth="1"/>
+    <col min="22" max="22" width="7.88671875" customWidth="1"/>
+    <col min="23" max="24" width="8.5546875" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="26" width="8.5546875" customWidth="1"/>
+    <col min="27" max="27" width="9.5546875" customWidth="1"/>
+    <col min="28" max="48" width="8.5546875" customWidth="1"/>
+    <col min="49" max="49" width="8.33203125" customWidth="1"/>
+    <col min="50" max="51" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:51" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
       <c r="AD1" s="2"/>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" ht="14.4" x14ac:dyDescent="0.3">
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="S2" s="3" t="s">
@@ -4759,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51" s="51" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" s="51" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="37" t="s">
         <v>1</v>
       </c>
@@ -4772,71 +4776,71 @@
       <c r="D3" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="112">
+      <c r="E3" s="169">
         <v>46113</v>
       </c>
-      <c r="F3" s="110"/>
-      <c r="G3" s="111"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161"/>
       <c r="H3" s="52"/>
       <c r="I3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="113">
+      <c r="J3" s="162">
         <v>46143</v>
       </c>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="111"/>
+      <c r="K3" s="160"/>
+      <c r="L3" s="160"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="161"/>
       <c r="O3" s="53"/>
       <c r="P3" s="53" t="s">
         <v>5</v>
       </c>
       <c r="Q3" s="54"/>
       <c r="R3" s="54"/>
-      <c r="S3" s="114">
+      <c r="S3" s="163">
         <v>46174</v>
       </c>
-      <c r="T3" s="110"/>
-      <c r="U3" s="110"/>
-      <c r="V3" s="110"/>
-      <c r="W3" s="110"/>
-      <c r="X3" s="110"/>
-      <c r="Y3" s="110"/>
-      <c r="Z3" s="111"/>
+      <c r="T3" s="160"/>
+      <c r="U3" s="160"/>
+      <c r="V3" s="160"/>
+      <c r="W3" s="160"/>
+      <c r="X3" s="160"/>
+      <c r="Y3" s="160"/>
+      <c r="Z3" s="161"/>
       <c r="AA3" s="54"/>
       <c r="AB3" s="54"/>
       <c r="AC3" s="55" t="s">
         <v>5</v>
       </c>
       <c r="AD3" s="56"/>
-      <c r="AE3" s="115">
+      <c r="AE3" s="164">
         <v>46204</v>
       </c>
-      <c r="AF3" s="110"/>
-      <c r="AG3" s="110"/>
-      <c r="AH3" s="111"/>
+      <c r="AF3" s="160"/>
+      <c r="AG3" s="160"/>
+      <c r="AH3" s="161"/>
       <c r="AI3" s="57"/>
       <c r="AJ3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="AK3" s="116">
+      <c r="AK3" s="165">
         <v>46235</v>
       </c>
-      <c r="AL3" s="110"/>
-      <c r="AM3" s="110"/>
-      <c r="AN3" s="110"/>
-      <c r="AO3" s="111"/>
+      <c r="AL3" s="160"/>
+      <c r="AM3" s="160"/>
+      <c r="AN3" s="160"/>
+      <c r="AO3" s="161"/>
       <c r="AP3" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="AQ3" s="109">
+      <c r="AQ3" s="159">
         <v>46266</v>
       </c>
-      <c r="AR3" s="110"/>
-      <c r="AS3" s="110"/>
-      <c r="AT3" s="110"/>
-      <c r="AU3" s="111"/>
+      <c r="AR3" s="160"/>
+      <c r="AS3" s="160"/>
+      <c r="AT3" s="160"/>
+      <c r="AU3" s="161"/>
       <c r="AV3" s="59" t="s">
         <v>5</v>
       </c>
@@ -4850,7 +4854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:51" s="51" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" s="51" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
         <v>9</v>
       </c>
@@ -4983,7 +4987,7 @@
       <c r="AX4" s="39"/>
       <c r="AY4" s="39"/>
     </row>
-    <row r="5" spans="1:51" s="51" customFormat="1" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" s="51" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="60" t="s">
         <v>13</v>
       </c>
@@ -5052,7 +5056,7 @@
       <c r="AX5" s="62"/>
       <c r="AY5" s="62"/>
     </row>
-    <row r="6" spans="1:51" s="28" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" s="28" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>17</v>
       </c>
@@ -5111,7 +5115,7 @@
       <c r="AX6" s="21"/>
       <c r="AY6" s="21"/>
     </row>
-    <row r="7" spans="1:51" s="28" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" s="28" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>20</v>
       </c>
@@ -5170,7 +5174,7 @@
       <c r="AX7" s="21"/>
       <c r="AY7" s="21"/>
     </row>
-    <row r="8" spans="1:51" s="28" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" s="28" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>21</v>
       </c>
@@ -5225,7 +5229,7 @@
       <c r="AX8" s="21"/>
       <c r="AY8" s="21"/>
     </row>
-    <row r="9" spans="1:51" s="28" customFormat="1" ht="51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" s="28" customFormat="1" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>23</v>
       </c>
@@ -5290,7 +5294,7 @@
       <c r="AX9" s="21"/>
       <c r="AY9" s="21"/>
     </row>
-    <row r="10" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>79</v>
       </c>
@@ -5345,7 +5349,7 @@
       <c r="AX10" s="21"/>
       <c r="AY10" s="21"/>
     </row>
-    <row r="11" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>78</v>
       </c>
@@ -5400,7 +5404,7 @@
       <c r="AX11" s="21"/>
       <c r="AY11" s="21"/>
     </row>
-    <row r="12" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>80</v>
       </c>
@@ -5455,7 +5459,7 @@
       <c r="AX12" s="21"/>
       <c r="AY12" s="21"/>
     </row>
-    <row r="13" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="20"/>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -5508,7 +5512,7 @@
       <c r="AX13" s="21"/>
       <c r="AY13" s="21"/>
     </row>
-    <row r="14" spans="1:51" s="28" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:51" s="28" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>28</v>
       </c>
@@ -5563,7 +5567,7 @@
       <c r="AX14" s="21"/>
       <c r="AY14" s="21"/>
     </row>
-    <row r="15" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>29</v>
       </c>
@@ -5624,7 +5628,7 @@
       <c r="AX15" s="21"/>
       <c r="AY15" s="21"/>
     </row>
-    <row r="16" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>30</v>
       </c>
@@ -5687,7 +5691,7 @@
       <c r="AX16" s="21"/>
       <c r="AY16" s="21"/>
     </row>
-    <row r="17" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>32</v>
       </c>
@@ -5742,7 +5746,7 @@
       <c r="AX17" s="21"/>
       <c r="AY17" s="21"/>
     </row>
-    <row r="18" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>33</v>
       </c>
@@ -5797,7 +5801,7 @@
       <c r="AX18" s="21"/>
       <c r="AY18" s="21"/>
     </row>
-    <row r="19" spans="1:51" s="28" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" s="28" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>34</v>
       </c>
@@ -5856,7 +5860,7 @@
       <c r="AX19" s="21"/>
       <c r="AY19" s="21"/>
     </row>
-    <row r="20" spans="1:51" s="28" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" s="28" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
         <v>35</v>
       </c>
@@ -5911,7 +5915,7 @@
       <c r="AX20" s="21"/>
       <c r="AY20" s="21"/>
     </row>
-    <row r="21" spans="1:51" s="28" customFormat="1" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" s="28" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>36</v>
       </c>
@@ -5974,7 +5978,7 @@
       <c r="AX21" s="21"/>
       <c r="AY21" s="21"/>
     </row>
-    <row r="22" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>39</v>
       </c>
@@ -6029,7 +6033,7 @@
       <c r="AX22" s="21"/>
       <c r="AY22" s="21"/>
     </row>
-    <row r="23" spans="1:51" s="28" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" s="28" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="20" t="s">
         <v>40</v>
       </c>
@@ -6088,7 +6092,7 @@
       <c r="AX23" s="21"/>
       <c r="AY23" s="21"/>
     </row>
-    <row r="24" spans="1:51" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" s="28" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>41</v>
       </c>
@@ -6143,7 +6147,7 @@
       <c r="AX24" s="21"/>
       <c r="AY24" s="21"/>
     </row>
-    <row r="25" spans="1:51" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
         <v>42</v>
       </c>
@@ -6198,7 +6202,7 @@
       <c r="AX25" s="21"/>
       <c r="AY25" s="21"/>
     </row>
-    <row r="26" spans="1:51" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" s="28" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
         <v>43</v>
       </c>
@@ -6253,7 +6257,7 @@
       <c r="AX26" s="21"/>
       <c r="AY26" s="21"/>
     </row>
-    <row r="27" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -6306,7 +6310,7 @@
       <c r="AX27" s="5"/>
       <c r="AY27" s="5"/>
     </row>
-    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -6359,29 +6363,29 @@
       <c r="AX28" s="5"/>
       <c r="AY28" s="5"/>
     </row>
-    <row r="29" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>45</v>
       </c>
       <c r="AV30" s="11"/>
     </row>
-    <row r="31" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>48</v>
       </c>
@@ -6389,124 +6393,124 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="L35" s="107" t="s">
+      <c r="L35" s="167" t="s">
         <v>51</v>
       </c>
-      <c r="M35" s="107"/>
-      <c r="N35" s="107"/>
-    </row>
-    <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M35" s="167"/>
+      <c r="N35" s="167"/>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>82</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="L36" s="107" t="s">
+      <c r="L36" s="167" t="s">
         <v>53</v>
       </c>
-      <c r="M36" s="107"/>
-      <c r="N36" s="107"/>
-    </row>
-    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M36" s="167"/>
+      <c r="N36" s="167"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="L37" s="107" t="s">
+      <c r="L37" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="M37" s="107"/>
-      <c r="N37" s="107"/>
-    </row>
-    <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M37" s="167"/>
+      <c r="N37" s="167"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>84</v>
       </c>
       <c r="B38" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L38" s="107" t="s">
+      <c r="L38" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="M38" s="107"/>
-      <c r="N38" s="107"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M38" s="167"/>
+      <c r="N38" s="167"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17" t="s">
         <v>85</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L39" s="107" t="s">
+      <c r="L39" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="M39" s="107"/>
-      <c r="N39" s="107"/>
-    </row>
-    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M39" s="167"/>
+      <c r="N39" s="167"/>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L40" s="107" t="s">
+      <c r="L40" s="167" t="s">
         <v>59</v>
       </c>
-      <c r="M40" s="107"/>
-      <c r="N40" s="107"/>
-    </row>
-    <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M40" s="167"/>
+      <c r="N40" s="167"/>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="L41" s="108" t="s">
+      <c r="L41" s="168" t="s">
         <v>94</v>
       </c>
-      <c r="M41" s="107"/>
-      <c r="N41" s="107"/>
-    </row>
-    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M41" s="167"/>
+      <c r="N41" s="167"/>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B42" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="L42" s="108" t="s">
+      <c r="L42" s="168" t="s">
         <v>94</v>
       </c>
-      <c r="M42" s="107"/>
-      <c r="N42" s="107"/>
-    </row>
-    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M42" s="167"/>
+      <c r="N42" s="167"/>
+    </row>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>89</v>
       </c>
       <c r="B43" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="L43" s="107" t="s">
+      <c r="L43" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="107"/>
-      <c r="N43" s="107"/>
-    </row>
-    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M43" s="167"/>
+      <c r="N43" s="167"/>
+    </row>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
         <v>90</v>
       </c>
@@ -6517,7 +6521,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>91</v>
       </c>
@@ -6528,1033 +6532,1025 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="17" t="s">
         <v>92</v>
       </c>
       <c r="B46" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="L46" s="107" t="s">
+      <c r="L46" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="M46" s="107"/>
-      <c r="N46" s="107"/>
-    </row>
-    <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M46" s="167"/>
+      <c r="N46" s="167"/>
+    </row>
+    <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>93</v>
       </c>
       <c r="B47" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="L47" s="107" t="s">
+      <c r="L47" s="167" t="s">
         <v>69</v>
       </c>
-      <c r="M47" s="107"/>
-      <c r="N47" s="107"/>
-    </row>
-    <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M47" s="167"/>
+      <c r="N47" s="167"/>
+    </row>
+    <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
         <v>70</v>
       </c>
       <c r="B48" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L48" s="107" t="s">
+      <c r="L48" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="M48" s="107"/>
-      <c r="N48" s="107"/>
-    </row>
-    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M48" s="167"/>
+      <c r="N48" s="167"/>
+    </row>
+    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
         <v>73</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L49" s="107" t="s">
+      <c r="L49" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="M49" s="107"/>
-      <c r="N49" s="107"/>
-    </row>
-    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M49" s="167"/>
+      <c r="N49" s="167"/>
+    </row>
+    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19" t="s">
         <v>75</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="L50" s="107" t="s">
+      <c r="L50" s="167" t="s">
         <v>55</v>
       </c>
-      <c r="M50" s="107"/>
-      <c r="N50" s="107"/>
-    </row>
-    <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="M50" s="167"/>
+      <c r="N50" s="167"/>
+    </row>
+    <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="L49:N49"/>
-    <mergeCell ref="L50:N50"/>
-    <mergeCell ref="L41:N41"/>
-    <mergeCell ref="L42:N42"/>
-    <mergeCell ref="L43:N43"/>
-    <mergeCell ref="L46:N46"/>
-    <mergeCell ref="L47:N47"/>
-    <mergeCell ref="L48:N48"/>
     <mergeCell ref="AK3:AO3"/>
     <mergeCell ref="AQ3:AU3"/>
     <mergeCell ref="L40:N40"/>
@@ -7567,6 +7563,14 @@
     <mergeCell ref="L37:N37"/>
     <mergeCell ref="L38:N38"/>
     <mergeCell ref="L39:N39"/>
+    <mergeCell ref="L49:N49"/>
+    <mergeCell ref="L50:N50"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="L46:N46"/>
+    <mergeCell ref="L47:N47"/>
+    <mergeCell ref="L48:N48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
